--- a/jyx2/Assets/Mods/SAMPLE/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/SAMPLE/Configs/人物.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -547,6 +547,9 @@
   </si>
   <si>
     <t>13,1|38,5</t>
+  </si>
+  <si>
+    <t>0,900|1,900|10,900|20,900|30,900|31,900|32,900|33,900|40,900|41,900|42,900|60,900|61,900|62,900|70,900|71,900|72,900|90,900|91,900|93,900|94,900|95,900|97,900|120,900|140,900|160,900|180,900|181,900|190,900</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="AN5" s="4" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="AO5" s="4" t="s">
         <v>160</v>
